--- a/data/2026-06-22/SCW Weekly Comp 2026-06-22 (Responses).xlsx
+++ b/data/2026-06-22/SCW Weekly Comp 2026-06-22 (Responses).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="283">
   <si>
     <t>Timestamp</t>
   </si>
@@ -827,6 +827,39 @@
   </si>
   <si>
     <t>https://www.facebook.com/events/856123937143434?post_id=866816599407501&amp;view=permalink</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/1307553804897425/?post_id=1317881533864652&amp;view=permalink&amp;__cft__[0]=AZZMVUqqKpJeVcbDCU21JiKwETCJSq2GaRC-w1L0Tlbqgf8OwcSVQUZrNs1C11ZV68tvCvK1Ad2CtJbawNxstV-e5sB12KkPIoRpKPQ-9enK2a9TgyKs8Fiq13ZC3tHpDlk&amp;__tn__=%2CO%2CP-R</t>
+  </si>
+  <si>
+    <t>8:07.17</t>
+  </si>
+  <si>
+    <t>6:46.12</t>
+  </si>
+  <si>
+    <t>Brad Deegan</t>
+  </si>
+  <si>
+    <t>2023DEEG01</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/2080772666174883/permalink/2088977998687683/?app=fbl</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/2080772666174883/permalink/2088976848687798/?app=fbl</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/2004459553776098/permalink/2010810623140991/?app=fbl</t>
+  </si>
+  <si>
+    <t>My best single here beat my in comp WCA single!</t>
+  </si>
+  <si>
+    <t>1:03.64</t>
+  </si>
+  <si>
+    <t>1:09.05</t>
   </si>
 </sst>
 </file>
@@ -983,7 +1016,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:DH44" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:DH48" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="112">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="Name" id="2"/>
@@ -3457,6 +3490,167 @@
         <v>133</v>
       </c>
     </row>
+    <row r="45" ht="22.5" customHeight="1">
+      <c r="A45" s="6">
+        <v>46210.73989532408</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="AO45" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="AP45" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="AQ45" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="AR45" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="AS45" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="46" ht="22.5" customHeight="1">
+      <c r="A46" s="6">
+        <v>46210.800865625</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="H46" s="7">
+        <v>7.31</v>
+      </c>
+      <c r="I46" s="7">
+        <v>9.38</v>
+      </c>
+      <c r="J46" s="7">
+        <v>8.46</v>
+      </c>
+      <c r="K46" s="7">
+        <v>8.2</v>
+      </c>
+      <c r="L46" s="7">
+        <v>13.78</v>
+      </c>
+      <c r="M46" s="7">
+        <v>7.31</v>
+      </c>
+      <c r="N46" s="7">
+        <v>8.68</v>
+      </c>
+    </row>
+    <row r="47" ht="22.5" customHeight="1">
+      <c r="A47" s="6">
+        <v>46210.80198546297</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="O47" s="7">
+        <v>21.09</v>
+      </c>
+      <c r="P47" s="7">
+        <v>23.83</v>
+      </c>
+      <c r="Q47" s="7">
+        <v>26.49</v>
+      </c>
+      <c r="R47" s="7">
+        <v>31.69</v>
+      </c>
+      <c r="S47" s="7">
+        <v>24.8</v>
+      </c>
+      <c r="T47" s="7">
+        <v>21.09</v>
+      </c>
+      <c r="U47" s="7">
+        <v>25.04</v>
+      </c>
+    </row>
+    <row r="48" ht="22.5" customHeight="1">
+      <c r="A48" s="6">
+        <v>46210.80344349537</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="BV48" s="7">
+        <v>55.67</v>
+      </c>
+      <c r="BW48" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="BX48" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="BY48" s="7">
+        <v>34.14</v>
+      </c>
+      <c r="BZ48" s="7">
+        <v>43.22</v>
+      </c>
+      <c r="CA48" s="7">
+        <v>34.14</v>
+      </c>
+      <c r="CB48" s="7">
+        <v>54.18</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="F2"/>
@@ -3502,10 +3696,14 @@
     <hyperlink r:id="rId41" ref="F42"/>
     <hyperlink r:id="rId42" ref="F43"/>
     <hyperlink r:id="rId43" ref="F44"/>
+    <hyperlink r:id="rId44" ref="F45"/>
+    <hyperlink r:id="rId45" ref="F46"/>
+    <hyperlink r:id="rId46" ref="F47"/>
+    <hyperlink r:id="rId47" ref="F48"/>
   </hyperlinks>
-  <drawing r:id="rId44"/>
+  <drawing r:id="rId48"/>
   <tableParts count="1">
-    <tablePart r:id="rId46"/>
+    <tablePart r:id="rId50"/>
   </tableParts>
 </worksheet>
 </file>